--- a/CPRD Raw Analysis/Results/Cohort/Output_overall_healthcare_roles-Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Cohort/Output_overall_healthcare_roles-Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,53 +375,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B2">
-        <v>368133</v>
+        <v>7405</v>
       </c>
       <c r="C2">
-        <v>40.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B3">
-        <v>361781</v>
+        <v>361678</v>
       </c>
       <c r="C3">
-        <v>40.13</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Dental</t>
         </is>
       </c>
       <c r="B4">
-        <v>87655</v>
+        <v>33</v>
       </c>
       <c r="C4">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B5">
-        <v>83966</v>
+        <v>361493</v>
       </c>
       <c r="C5">
-        <v>9.31</v>
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Medic non-GP</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3122</v>
+      </c>
+      <c r="C6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Non-registered other</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>122532</v>
+      </c>
+      <c r="C7">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>44904</v>
+      </c>
+      <c r="C8">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>334</v>
+      </c>
+      <c r="C9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>34</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -459,34 +524,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Appointments Clerk</t>
+          <t>Art Therapist</t>
         </is>
       </c>
       <c r="C2">
-        <v>1649</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Asst. Clinical Medical Officer</t>
+          <t>Art Therapist Consultant</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -495,16 +560,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Availability Monitor</t>
+          <t>Art Therapist Manager</t>
         </is>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -513,160 +578,160 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caldicott Guardian</t>
+          <t>Art Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="C5">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clerical Worker</t>
+          <t>Audiologist</t>
         </is>
       </c>
       <c r="C6">
-        <v>46096</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>5.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clinical Application Administrator</t>
+          <t>Biomedical Scientist</t>
         </is>
       </c>
       <c r="C7">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clinical Coder</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="C8">
-        <v>3942</v>
+        <v>111</v>
       </c>
       <c r="D8">
-        <v>0.44</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Community Administrator</t>
+          <t>Chiropodist/Podiatrist Consultant</t>
         </is>
       </c>
       <c r="C9">
-        <v>22350</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>2.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Desktop Support Administrator</t>
+          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
         </is>
       </c>
       <c r="C10">
-        <v>21074</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>2.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desktop Support Technician</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="C11">
-        <v>938</v>
+        <v>79</v>
       </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dispenser</t>
+          <t>Dietitian Manager</t>
         </is>
       </c>
       <c r="C12">
-        <v>5292</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finance Director</t>
+          <t>Dietitian Specialist Practitioner</t>
         </is>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -675,250 +740,250 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Health Records Administrator</t>
+          <t>Intermediate Care staff</t>
         </is>
       </c>
       <c r="C14">
-        <v>509</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Health Records Clerk</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="C15">
-        <v>381</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Helpdesk Administrator</t>
+          <t>Multi Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="C16">
-        <v>1059</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Helpdesk Technician</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="C17">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Helper/Assistant</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="C18">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Information Officer</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="C19">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="D19">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="C20">
-        <v>73922</v>
+        <v>211</v>
       </c>
       <c r="D20">
-        <v>8.199999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medical Records Clerk</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="C21">
-        <v>918</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Medical Records Manager</t>
+          <t>Paramedic Manager</t>
         </is>
       </c>
       <c r="C22">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="D22">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Medical Secretary</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="C23">
-        <v>14165</v>
+        <v>217</v>
       </c>
       <c r="D23">
-        <v>1.57</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Network Administrator</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="C24">
-        <v>616</v>
+        <v>5510</v>
       </c>
       <c r="D24">
-        <v>0.07000000000000001</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Network Technician</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="C25">
-        <v>304</v>
+        <v>474</v>
       </c>
       <c r="D25">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Admin Clerk</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="C26">
-        <v>576</v>
+        <v>19</v>
       </c>
       <c r="D26">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Porter</t>
+          <t>Physiotherapist Manager</t>
         </is>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -927,120 +992,120 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Receptionist</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="C28">
-        <v>90210</v>
+        <v>24</v>
       </c>
       <c r="D28">
-        <v>10.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>Pre-reg Pharmacist</t>
         </is>
       </c>
       <c r="C29">
-        <v>12271</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Senior Administrator</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="C30">
-        <v>16046</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>1.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Radiographer</t>
         </is>
       </c>
       <c r="C31">
-        <v>3567</v>
+        <v>28</v>
       </c>
       <c r="D31">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Radiographer - Diagnostic</t>
         </is>
       </c>
       <c r="C32">
-        <v>48268</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>5.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>System Worker</t>
+          <t>Radiographer - Diagnostic, Manager</t>
         </is>
       </c>
       <c r="C33">
-        <v>1032</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Technician - Additional Clinical Services</t>
+          <t>Radiographer - Diagnostic, Specialist Practitioner</t>
         </is>
       </c>
       <c r="C34">
@@ -1053,52 +1118,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Technician - Admin &amp; Clerical</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="C35">
-        <v>1226</v>
+        <v>49</v>
       </c>
       <c r="D35">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Waiting List Manager</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="C36">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ward Clerk</t>
+          <t>Student Physiotherapist</t>
         </is>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1107,358 +1172,358 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Technician - Healthcare Scientists</t>
         </is>
       </c>
       <c r="C38">
-        <v>2122</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="C39">
-        <v>11921</v>
+        <v>51</v>
       </c>
       <c r="D39">
-        <v>1.32</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C40">
-        <v>303981</v>
+        <v>75</v>
       </c>
       <c r="D40">
-        <v>33.72</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Appointments Clerk</t>
         </is>
       </c>
       <c r="C41">
-        <v>4765</v>
+        <v>1649</v>
       </c>
       <c r="D41">
-        <v>0.53</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Availability Monitor</t>
         </is>
       </c>
       <c r="C42">
-        <v>288</v>
+        <v>35</v>
       </c>
       <c r="D42">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Call Operator</t>
         </is>
       </c>
       <c r="C43">
-        <v>26363</v>
+        <v>21</v>
       </c>
       <c r="D43">
-        <v>2.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Clerical Worker</t>
         </is>
       </c>
       <c r="C44">
-        <v>12341</v>
+        <v>46096</v>
       </c>
       <c r="D44">
-        <v>1.37</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Clinical Application Administrator</t>
         </is>
       </c>
       <c r="C45">
-        <v>1950</v>
+        <v>606</v>
       </c>
       <c r="D45">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Clinical Coder</t>
         </is>
       </c>
       <c r="C46">
-        <v>15343</v>
+        <v>3942</v>
       </c>
       <c r="D46">
-        <v>1.7</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Clinical Team Manager</t>
         </is>
       </c>
       <c r="C47">
-        <v>43287</v>
+        <v>12</v>
       </c>
       <c r="D47">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>Community Administrator</t>
         </is>
       </c>
       <c r="C48">
-        <v>1590</v>
+        <v>22350</v>
       </c>
       <c r="D48">
-        <v>0.18</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Community Team Manager</t>
         </is>
       </c>
       <c r="C49">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="D49">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Desktop Support Administrator</t>
         </is>
       </c>
       <c r="C50">
-        <v>1580</v>
+        <v>21074</v>
       </c>
       <c r="D50">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nurse Manager</t>
+          <t>Desktop Support Technician</t>
         </is>
       </c>
       <c r="C51">
-        <v>2122</v>
+        <v>938</v>
       </c>
       <c r="D51">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Finance Director</t>
         </is>
       </c>
       <c r="C52">
-        <v>2480</v>
+        <v>26</v>
       </c>
       <c r="D52">
-        <v>0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Health Records Administrator</t>
         </is>
       </c>
       <c r="C53">
-        <v>11985</v>
+        <v>509</v>
       </c>
       <c r="D53">
-        <v>1.33</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Staff Nurse</t>
+          <t>Health Records Clerk</t>
         </is>
       </c>
       <c r="C54">
-        <v>7071</v>
+        <v>381</v>
       </c>
       <c r="D54">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Student Practice Nurse</t>
+          <t>Helpdesk Administrator</t>
         </is>
       </c>
       <c r="C55">
-        <v>32</v>
+        <v>1059</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ward Manager</t>
+          <t>Helpdesk Technician</t>
         </is>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Advanced Practitioner</t>
+          <t>Information Officer</t>
         </is>
       </c>
       <c r="C57">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="D57">
         <v>0.03</v>
@@ -1467,268 +1532,268 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C58">
-        <v>75</v>
+        <v>73922</v>
       </c>
       <c r="D58">
-        <v>0.01</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Art Therapist</t>
+          <t>Medical Records Clerk</t>
         </is>
       </c>
       <c r="C59">
-        <v>50</v>
+        <v>918</v>
       </c>
       <c r="D59">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Art Therapist Consultant</t>
+          <t>Medical Records Manager</t>
         </is>
       </c>
       <c r="C60">
-        <v>9</v>
+        <v>280</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Art Therapist Manager</t>
+          <t>Medical Secretary</t>
         </is>
       </c>
       <c r="C61">
-        <v>32</v>
+        <v>14165</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Art Therapist Specialist Practitioner</t>
+          <t>Network Administrator</t>
         </is>
       </c>
       <c r="C62">
-        <v>16</v>
+        <v>616</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Assistant GP</t>
+          <t>Network Technician</t>
         </is>
       </c>
       <c r="C63">
-        <v>125</v>
+        <v>304</v>
       </c>
       <c r="D63">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Other Community Health Service - Admin Clerk</t>
         </is>
       </c>
       <c r="C64">
-        <v>450</v>
+        <v>576</v>
       </c>
       <c r="D64">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Associate Practitioner</t>
+          <t>Outpatient Manager</t>
         </is>
       </c>
       <c r="C65">
-        <v>294</v>
+        <v>8</v>
       </c>
       <c r="D65">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Receptionist</t>
         </is>
       </c>
       <c r="C66">
-        <v>192</v>
+        <v>90210</v>
       </c>
       <c r="D66">
-        <v>0.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Audiologist</t>
+          <t>Secretary</t>
         </is>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>12271</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Biomedical Scientist</t>
+          <t>Senior Administrator</t>
         </is>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>16046</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Call Operator</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>3567</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Child Protection worker</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="C70">
-        <v>22</v>
+        <v>48268</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Technician - Admin &amp; Clerical</t>
         </is>
       </c>
       <c r="C71">
-        <v>111</v>
+        <v>1226</v>
       </c>
       <c r="D71">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist Consultant</t>
+          <t>Waiting List Manager</t>
         </is>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1737,16 +1802,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
+          <t>Ward Clerk</t>
         </is>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1755,34 +1820,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Ward Manager</t>
         </is>
       </c>
       <c r="C74">
-        <v>542</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Dental</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Clinical Director</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -1791,142 +1856,142 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Clinical Director - Medical</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="C76">
-        <v>89</v>
+        <v>2122</v>
       </c>
       <c r="D76">
-        <v>0.01</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Clinical Medical Officer</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>11921</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="C78">
-        <v>8</v>
+        <v>303981</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Clinical Team Manager</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="C79">
-        <v>12</v>
+        <v>4765</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="C80">
-        <v>90</v>
+        <v>26363</v>
       </c>
       <c r="D80">
-        <v>0.01</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Community Team Manager</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="C81">
-        <v>13</v>
+        <v>12341</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Asst. Clinical Medical Officer</t>
         </is>
       </c>
       <c r="C82">
-        <v>2046</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Caldicott Guardian</t>
         </is>
       </c>
       <c r="C83">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D83">
         <v>0.01</v>
@@ -1935,34 +2000,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deputising Doctor</t>
+          <t>Clinical Director</t>
         </is>
       </c>
       <c r="C84">
-        <v>174</v>
+        <v>8</v>
       </c>
       <c r="D84">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>Clinical Director - Medical</t>
         </is>
       </c>
       <c r="C85">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D85">
         <v>0.01</v>
@@ -1971,12 +2036,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dietitian Manager</t>
+          <t>Clinical Medical Officer</t>
         </is>
       </c>
       <c r="C86">
@@ -1989,88 +2054,88 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2046</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Director of Nursing</t>
+          <t>Deputising Doctor</t>
         </is>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="C89">
-        <v>37858</v>
+        <v>24</v>
       </c>
       <c r="D89">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>House Officer - Post Registration</t>
         </is>
       </c>
       <c r="C90">
-        <v>25945</v>
+        <v>113</v>
       </c>
       <c r="D90">
-        <v>2.88</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Healthcare Cadet</t>
+          <t>House Officer - Pre Registration</t>
         </is>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -2079,52 +2144,52 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Medical Student</t>
         </is>
       </c>
       <c r="C92">
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>House Officer - Post Registration</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="C93">
-        <v>113</v>
+        <v>288</v>
       </c>
       <c r="D93">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>House Officer - Pre Registration</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -2133,16 +2198,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intermediate Care staff</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="C95">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -2151,34 +2216,34 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Medical Student</t>
+          <t>Trust Grade Doctor - SHO level</t>
         </is>
       </c>
       <c r="C96">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="D96">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Assistant GP</t>
         </is>
       </c>
       <c r="C97">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="D97">
         <v>0.01</v>
@@ -2187,124 +2252,124 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Assistant Practitioner</t>
         </is>
       </c>
       <c r="C98">
-        <v>837</v>
+        <v>450</v>
       </c>
       <c r="D98">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Associate Practitioner</t>
         </is>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>294</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Clinical Assistant</t>
         </is>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>542</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="C102">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="D102">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>43287</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="C104">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D104">
         <v>0.01</v>
@@ -2313,169 +2378,169 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Dispenser</t>
         </is>
       </c>
       <c r="C105">
-        <v>334</v>
+        <v>5292</v>
       </c>
       <c r="D105">
-        <v>0.04</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>37858</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Outpatient Manager</t>
+          <t>Healthcare Assistant</t>
         </is>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>25945</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Healthcare Cadet</t>
         </is>
       </c>
       <c r="C108">
-        <v>211</v>
+        <v>6</v>
       </c>
       <c r="D108">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Helper/Assistant</t>
         </is>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Paramedic Manager</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="C110">
-        <v>198</v>
+        <v>67</v>
       </c>
       <c r="D110">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="C111">
-        <v>217</v>
+        <v>837</v>
       </c>
       <c r="D111">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="C113">
-        <v>5510</v>
+        <v>3</v>
       </c>
       <c r="D113">
-        <v>0.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2493,7 +2558,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2511,34 +2576,34 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Porter</t>
         </is>
       </c>
       <c r="C116">
-        <v>474</v>
+        <v>21</v>
       </c>
       <c r="D116">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="C117">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2547,16 +2612,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Physiotherapist Manager</t>
+          <t>Student Community Practitioner</t>
         </is>
       </c>
       <c r="C118">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2565,34 +2630,34 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>System Worker</t>
         </is>
       </c>
       <c r="C119">
-        <v>24</v>
+        <v>1032</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Technician - Additional Clinical Services</t>
         </is>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -2601,223 +2666,223 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="C121">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Radiographer</t>
+          <t>Advanced Practitioner</t>
         </is>
       </c>
       <c r="C122">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>1950</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic, Manager</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="C124">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic, Specialist Practitioner</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>15343</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Director of Nursing</t>
         </is>
       </c>
       <c r="C126">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D126">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="C127">
-        <v>33</v>
+        <v>1590</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="C128">
-        <v>25</v>
+        <v>212</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="C129">
-        <v>28</v>
+        <v>1580</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Nurse Manager</t>
         </is>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>2122</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Specialist Practitioner</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="C131">
-        <v>135</v>
+        <v>2480</v>
       </c>
       <c r="D131">
-        <v>0.01</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Specialist Registrar</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>11985</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2835,25 +2900,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Student Community Practitioner</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="C134">
-        <v>9</v>
+        <v>7071</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2871,7 +2936,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2889,16 +2954,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Student Physiotherapist</t>
+          <t>Student Practice Nurse</t>
         </is>
       </c>
       <c r="C137">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2907,70 +2972,70 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Technician - Healthcare Scientists</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>334</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Therapist</t>
+          <t>Child Protection worker</t>
         </is>
       </c>
       <c r="C139">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D139">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Trainee Practitioner</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="C140">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D140">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Trust Grade Doctor - SHO level</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="C141">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D141">
         <v>0</v>
